--- a/桌面轮足/购买清单/桌面轮足Bom表.xlsx
+++ b/桌面轮足/购买清单/桌面轮足Bom表.xlsx
@@ -188,9 +188,6 @@
     <t>JDY-33蓝牙从机模块</t>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?_u=b2085qbuhef29d&amp;id=618317697790&amp;pisk=fRkqoq6ElKpVjkvHloyNUGJaA7VYH-YBSAa_jcmgcr4D6o9GQco3fnL9Dbri54K9D-ig7Vu7yOZ6MFBZzqinGSgsGPqgr4mfhP9Y_VoIJV66HjZGQ4iTsVMZXOrijVKY5nKSDmeTIeTQQpixDcX8SzDVILVo2ofGo3hDIX2TIeTBdpixDR3LmkjUo_quyo7ciVVcE0qTrlf0IV4uZkqCoR0gI35ujlZGS54iq3rUbNX0itfkEkqdmP0gI3SuXXanSqBzzSxK58rQKHKUGym0oisjnGPfMmUyAHHPd1UEm1BGIYr4MAtXMeYaGfmL9xiWQTejYb2uAmpVUJm0YqaS-pXzE0io5WhJW9wjzAPrI7JhzuhocfDxuGWgDxMQ_yFyjOF_EvNn_R8RauGixYPnEhsU5XiSn7uHPTuT_Xn_bqJVn2jPqNEorektgNfgiOZzR3-rjG_urar8e75O67R84ytpv1fGJ961gAtA61FymuzBvnf..&amp;skuId=4590057118482&amp;spm=a1z09.2.0.0.9ead2e8d3vUIM7</t>
-  </si>
-  <si>
     <t>STM32 H723开发板</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -223,6 +220,10 @@
   </si>
   <si>
     <t>https://gitee.com/kit-miao/damiao/tree/master/%E5%85%B3%E8%8A%82%E7%94%B5%E6%9C%BA/DM-J3507-2EC/%E8%BD%AC%E6%8E%A5%E6%9D%BF/SH1.0%E8%BD%ACXT30%20+GH1.25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?_u=b2085qbuhef29d&amp;id=618317697790&amp;pisk=fRkqoq6ElKpVjkvHloyNUGJaA7VYH-YBSAa_jcmgcr4D6o9GQco3fnL9Dbri54K9D-ig7Vu7yOZ6MFBZzqinGSgsGPqgr4mfhP9Y_VoIJV66HjZGQ4iTsVMZXOrijVKY5nKSDmeTIeTQQpixDcX8SzDVILVo2ofGo3hDIX2TIeTBdpixDR3LmkjUo_quyo7ciVVcE0qTrlf0IV4uZkqCoR0gI35ujlZGS54iq3rUbNX0itfkEkqdmP0gI3SuXXanSqBzzSxK58rQKHKUGym0oisjnGPfMmUyAHHPd1UEm1BGIYr4MAtXMeYaGfmL9xiWQTejYb2uAmpVUJm0YqaS-pXzE0io5WhJW9wjzAPrI7JhzuhocfDxuGWgDxMQ_yFyjOF_EvNn_R8RauGixYPnEhsU5XiSn7uHPTuT_Xn_bqJVn2jPqNEorektgNfgiOZzR3-rjG_urar8e75O67R84ytpv1fGJ961gAtA61FymuzBvnf..&amp;skuId=4590057118482&amp;spm=a1z09.2.0.0.9ead2e8d3vUIM7</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -862,7 +863,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:colOff>12701</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
@@ -917,7 +918,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>601593</xdr:colOff>
+      <xdr:colOff>601592</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>61290</xdr:rowOff>
     </xdr:to>
@@ -1220,7 +1221,7 @@
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.54296875" customWidth="1"/>
-    <col min="2" max="2" width="54.81640625" customWidth="1"/>
+    <col min="2" max="2" width="83.7265625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="5" max="5" width="38.54296875" customWidth="1"/>
     <col min="10" max="10" width="19.26953125" customWidth="1"/>
@@ -1230,7 +1231,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1261,7 +1262,7 @@
         <v>46</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1729,7 +1730,7 @@
         <v>37</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>36</v>
@@ -1764,10 +1765,10 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>36</v>
@@ -1812,7 +1813,7 @@
         <v>43</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>42</v>
@@ -1838,7 +1839,7 @@
         <v>44</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>45</v>
@@ -1893,8 +1894,8 @@
       <c r="A33" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="28" t="s">
-        <v>52</v>
+      <c r="B33" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>51</v>
@@ -1914,10 +1915,10 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="28" t="s">
         <v>57</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>58</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8">
@@ -2167,7 +2168,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B24" display="https://item.taobao.com/item.htm?id=855508643710&amp;pisk=fJQyrj0czzUyVu2SfL8Eu7QuI_TJSFe_aw9Bt6fHNLvkFw6FtCdKqB0kZK4DsKgQwUZp89JVpLtWrwSx81CdP7LQwUCJJe2_CPTFw_LdGeb9EazDnQCDtDAhtzDkRe2_Cyoji3eW-T_8DHnWmKdet20hKnvDNKAkteXHnnAMt4YH-URF1WFbf3eGnKjpOTG2zlNBn20hr"/>
+    <hyperlink ref="B24"/>
     <hyperlink ref="B3" r:id="rId1" display="https://detail.tmall.com/item.htm?id=693377485791&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe5af5&amp;pisk=fqcm0vmBNxybPaQ9mbVXB7WCS8v-GiNs_cCTX5EwUurW5tBvlRzZScctHVrTscmijoewcShiq2g9lfLbgC4Zv0VtkoEtqFmx51KXCSCNjmgecqE9lfqaqmogCEZTblmt7xLJ9B3jl5NajHdp9y1-Vqmc_5W277zY5Y3VHwujl5ZNyGJKUq6M0z8s_Roaa8zao5z4bPuyrP41_5r4QgWz8ura_5oaaTzLoiSabrPzzbUA3khZLb-4KNn9zfWZkr20j1ElsmcC9Rqe2u5Gso0_nx34q15ZZY9jqWq2daE_Mog4ocOCGSyiQjFrg3RaTviosJPHBEwqSYm_Mb8N3kkxDRGuEiW4-Sq0LjyD1ENzQYcuMj-1d43u0JV-eLtYBSmmdkw2F3iironZi8SD2lHKyjyoY3CofRDZM7l24BjyzTWEyC1_zFhPCOw4PzqILGGF55gxHH8kr93_3zaQvUYlCD24Pr22rUXCS-z7on5.."/>
     <hyperlink ref="B19" r:id="rId2" display="https://detail.tmall.com/item.htm?id=617808114995&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe67ee&amp;pisk=fhYx0Zby0YDc-RiMlIilSjrdm_hlHEd2aKRQSOX0fLpJBBFDmGXGfNpepGai0ZjOWL6kotAcl1s6IptchnXgWFpyHr4Gld0OCB-r_tfDo5C6VKUMmIXD25Q2rn4Gnx791pbtKv0n-IRVbNMnKv1q6V_C_Sa_IGg5PJXYiDgn-IR8isGHN2cZpLsCd1_1cG6SPT5T5l_6Cg65OTaf1r1_FbCNFO_1c1aSP61b5osfCbEEMTPfMPK6W87Z94ijBALRNAWBMr4l6F1Yv9AcevaJyeSAdI685v4y1p6OUeMo2QJpcKfyB2HRRHJJWM_tkJ5vVBQ5nwiL2Zdk3eQXJxUcZaX5Ahs-GqORktI1gM3thZK63FI2D5leNZ9yY9Sj4Y5JoejOLgeShQARhMK9nYz1nHdWeMYuEybBYLLOAwsPUeYpkgyhp1qjwbEabi1uAcUuE7iHabCRKjsbblSGa_BnwTrabg_Ow9cxLlrNVfC..&amp;skuId=4355692940487"/>
     <hyperlink ref="B6" r:id="rId3" display="https://detail.tmall.com/item.htm?id=534828257082&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhef350&amp;pisk=fsSS01AcEbc5kS6XtUe2l6gazy-CN_Zavv9dI9nrp3KJRDBP1poe8zvIAI6TEQz3r6_f9sYywB8eAp1wiToUETyQA9B9wH7yapCVOs0PaMRFgk6G1UoPpMklo1Wt4gzkYDtkxHFa_lrNUTxHvG0lT4lkHdvaY0nJe4ZfU-Pa_lrQyxKQN57FMbKkhpOvepd-y-tvIdRpvedJD-9pLb3K26BYhpAve2p-yjHvId9-vbEmGpzWpTwxDU7gw8cGPIiKfAvWy5Wq8ci_cLYk6EKqv-SXFUOOegjeqppA0iTwuvP2DObVwKt_Vfv5kOtJdM2tRBTCqnOf1lnHnaC5Des4KlBJVpT9vEMKvttfzEpWXlhXnZBPJgfSdDpl4G8BsEwKxe-AbFQONv2GH3pdtFjUs0ARpOjG7hZSsL_ACnsz_cRsr10IhFmBhCybh20EduI2b5lh2NTJnLEah-Gj-UpDhRebhV4ByKvWe-wjS61.."/>
@@ -2187,6 +2188,7 @@
     <hyperlink ref="B27" r:id="rId17" display="https://item.taobao.com/item.htm?abbucket=19&amp;id=814954787248&amp;ns=1&amp;pisk=gZVE38AgT6CeSVNFqVcygDYnP_cKNXjfT7iSrz4oRDmnAz0oalq5JDalvuPrjzeCJYspzeFa0QOCv9UkabGlci1fGyUIwbjfZ_AE6H3jrLfWK0Di94MdfNt1GyUK2bjfcs1X4UjoPHvoquciI4ujZ2Do-hbZPqtoZDDkjd0mj0cuqDDMS4geqHDHKVbZJ4Rk-2mkjF0mPQxuqbbaSc3oNrruvCoZKa2xEZOOKDkEmymwgPFZ-S9L8cWOC5yZLmAjbQAu_24MLRKWgTi0HDMjmlf6TbzizlkbLiRU4z4YEAPyxwZ0j8roWRIyUmyuR-FtKUv377oEnWDwoZU4-4qoURI2G2lQQxPUpaKg-oiUnXUWuMaZ3RkxSAYyKXwbl7H0t6-xfx3zbxwF0Brc45x-SvqbwJ-kUv0t7m_N7Ub6flrMRIJMeLHNBVofkZpJev0t7m_N7Lp-Q53ZcZQA.&amp;priceTId=2147bf9717359593441207149edb5a&amp;skuId=5681498675796&amp;spm=a21n57.1.item.7.6260523c5GH0CB&amp;utparam=%7B%22aplus_abtest%22%3A%225e85845e3a5c91a409b05727b287b8ef%22%7D&amp;xxc=taobaoSearch"/>
     <hyperlink ref="B29" r:id="rId18"/>
     <hyperlink ref="B30" r:id="rId19"/>
+    <hyperlink ref="B33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId20"/>
